--- a/reports/test5_summary.xlsx
+++ b/reports/test5_summary.xlsx
@@ -279,11 +279,14 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E21</f>
+              <f>'Table 1'!E22</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -297,12 +300,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$22:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -311,11 +314,14 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E22</f>
+              <f>'Table 1'!E23</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -329,12 +335,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$22:$I$22</f>
+              <f>'Table 1'!$F$23:$G$23</f>
             </numRef>
           </val>
         </ser>
@@ -343,11 +349,14 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E23</f>
+              <f>'Table 1'!E24</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -361,12 +370,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$23:$I$23</f>
+              <f>'Table 1'!$F$24:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -375,11 +384,14 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E24</f>
+              <f>'Table 1'!E25</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -393,12 +405,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$24:$I$24</f>
+              <f>'Table 1'!$F$25:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -407,11 +419,14 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E25</f>
+              <f>'Table 1'!E26</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -425,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$25:$I$25</f>
+              <f>'Table 1'!$F$26:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -439,11 +454,14 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Table 1'!E26</f>
+              <f>'Table 1'!E27</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -457,44 +475,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
+              <f>'Table 1'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 1'!$F$26:$I$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'Table 1'!E27</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Table 1'!$F$21:$I$21</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Table 1'!$F$27:$I$27</f>
+              <f>'Table 1'!$F$27:$G$27</f>
             </numRef>
           </val>
         </ser>
@@ -506,6 +492,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -524,6 +511,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -531,7 +519,10 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="-8.710000000000001"/>
+          <min val="-11.71"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -551,6 +542,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -590,11 +582,14 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Table 2'!E21</f>
+              <f>'Table 2'!E22</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -608,12 +603,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 2'!$F$21:$I$21</f>
+              <f>'Table 2'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 2'!$F$21:$I$21</f>
+              <f>'Table 2'!$F$22:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -622,11 +617,14 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Table 2'!E22</f>
+              <f>'Table 2'!E23</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -640,12 +638,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 2'!$F$21:$I$21</f>
+              <f>'Table 2'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 2'!$F$22:$I$22</f>
+              <f>'Table 2'!$F$23:$G$23</f>
             </numRef>
           </val>
         </ser>
@@ -654,11 +652,14 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Table 2'!E23</f>
+              <f>'Table 2'!E24</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -672,12 +673,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 2'!$F$21:$I$21</f>
+              <f>'Table 2'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 2'!$F$23:$I$23</f>
+              <f>'Table 2'!$F$24:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -686,11 +687,14 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Table 2'!E24</f>
+              <f>'Table 2'!E25</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -704,12 +708,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 2'!$F$21:$I$21</f>
+              <f>'Table 2'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 2'!$F$24:$I$24</f>
+              <f>'Table 2'!$F$25:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -718,11 +722,14 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Table 2'!E25</f>
+              <f>'Table 2'!E26</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -736,44 +743,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 2'!$F$21:$I$21</f>
+              <f>'Table 2'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 2'!$F$25:$I$25</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'Table 2'!E26</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Table 2'!$F$21:$I$21</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Table 2'!$F$26:$I$26</f>
+              <f>'Table 2'!$F$26:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -785,6 +760,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -803,6 +779,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -810,7 +787,10 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="-8.57"/>
+          <min val="-11.38"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -830,6 +810,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -869,11 +850,14 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Table 3'!E21</f>
+              <f>'Table 3'!E22</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F497D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -887,12 +871,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 3'!$F$21:$I$21</f>
+              <f>'Table 3'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 3'!$F$21:$I$21</f>
+              <f>'Table 3'!$F$22:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -901,11 +885,14 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Table 3'!E22</f>
+              <f>'Table 3'!E23</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -919,12 +906,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 3'!$F$21:$I$21</f>
+              <f>'Table 3'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 3'!$F$22:$I$22</f>
+              <f>'Table 3'!$F$23:$G$23</f>
             </numRef>
           </val>
         </ser>
@@ -933,11 +920,14 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Table 3'!E23</f>
+              <f>'Table 3'!E24</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -951,12 +941,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 3'!$F$21:$I$21</f>
+              <f>'Table 3'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 3'!$F$23:$I$23</f>
+              <f>'Table 3'!$F$24:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -965,11 +955,14 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Table 3'!E24</f>
+              <f>'Table 3'!E25</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -983,12 +976,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 3'!$F$21:$I$21</f>
+              <f>'Table 3'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 3'!$F$24:$I$24</f>
+              <f>'Table 3'!$F$25:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -997,11 +990,14 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Table 3'!E25</f>
+              <f>'Table 3'!E26</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1015,12 +1011,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 3'!$F$21:$I$21</f>
+              <f>'Table 3'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 3'!$F$25:$I$25</f>
+              <f>'Table 3'!$F$26:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -1029,11 +1025,14 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Table 3'!E26</f>
+              <f>'Table 3'!E27</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1047,12 +1046,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 3'!$F$21:$I$21</f>
+              <f>'Table 3'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 3'!$F$26:$I$26</f>
+              <f>'Table 3'!$F$27:$G$27</f>
             </numRef>
           </val>
         </ser>
@@ -1061,11 +1060,14 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'Table 3'!E27</f>
+              <f>'Table 3'!E28</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E26B0A"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1079,44 +1081,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Table 3'!$F$21:$I$21</f>
+              <f>'Table 3'!$F$21:$G$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Table 3'!$F$27:$I$27</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'Table 3'!E28</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Table 3'!$F$21:$I$21</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Table 3'!$F$28:$I$28</f>
+              <f>'Table 3'!$F$28:$G$28</f>
             </numRef>
           </val>
         </ser>
@@ -1128,6 +1098,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <title>
           <tx>
@@ -1146,6 +1117,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1153,7 +1125,10 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="-8.67"/>
+          <min val="-11.67"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1173,6 +1148,7 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -1555,7 +1531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1565,8 +1541,6 @@
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1859,12 +1833,6 @@
         <v>3</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" s="11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1895,14 +1863,6 @@
         <v/>
       </c>
       <c r="G22" s="15">
-        <f>C22-D22*4</f>
-        <v/>
-      </c>
-      <c r="H22" s="15">
-        <f>C22-D22*5</f>
-        <v/>
-      </c>
-      <c r="I22" s="15">
         <f>C22-D22*6</f>
         <v/>
       </c>
@@ -1934,14 +1894,6 @@
         <v/>
       </c>
       <c r="G23" s="15">
-        <f>C23-D23*4</f>
-        <v/>
-      </c>
-      <c r="H23" s="15">
-        <f>C23-D23*5</f>
-        <v/>
-      </c>
-      <c r="I23" s="15">
         <f>C23-D23*6</f>
         <v/>
       </c>
@@ -1973,14 +1925,6 @@
         <v/>
       </c>
       <c r="G24" s="15">
-        <f>C24-D24*4</f>
-        <v/>
-      </c>
-      <c r="H24" s="15">
-        <f>C24-D24*5</f>
-        <v/>
-      </c>
-      <c r="I24" s="15">
         <f>C24-D24*6</f>
         <v/>
       </c>
@@ -2012,14 +1956,6 @@
         <v/>
       </c>
       <c r="G25" s="15">
-        <f>C25-D25*4</f>
-        <v/>
-      </c>
-      <c r="H25" s="15">
-        <f>C25-D25*5</f>
-        <v/>
-      </c>
-      <c r="I25" s="15">
         <f>C25-D25*6</f>
         <v/>
       </c>
@@ -2051,14 +1987,6 @@
         <v/>
       </c>
       <c r="G26" s="15">
-        <f>C26-D26*4</f>
-        <v/>
-      </c>
-      <c r="H26" s="15">
-        <f>C26-D26*5</f>
-        <v/>
-      </c>
-      <c r="I26" s="15">
         <f>C26-D26*6</f>
         <v/>
       </c>
@@ -2090,14 +2018,6 @@
         <v/>
       </c>
       <c r="G27" s="15">
-        <f>C27-D27*4</f>
-        <v/>
-      </c>
-      <c r="H27" s="15">
-        <f>C27-D27*5</f>
-        <v/>
-      </c>
-      <c r="I27" s="15">
         <f>C27-D27*6</f>
         <v/>
       </c>
@@ -2107,7 +2027,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>EXTRACTED TABLE DATA</t>
+          <t>EXTRACTED RAW TABLE DATA</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -2140,151 +2060,127 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>benzene, [11]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>pMA</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>toluene, [13]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>pMMA</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>CDCl 3 , [11]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>dextrane</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>D 2 O, [11]</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
       <c r="A36" s="13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>pullane</t>
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>benzene, [11]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>pMA</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="D41" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>toluene, [13]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>pMMA</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="D46" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>CDCl 3 , [11]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>dextrane</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="D51" s="13" t="n">
+          <t>D 2 O, [15]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>PEG [a]</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="D37" s="13" t="n">
         <v>0.47</v>
       </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>D 2 O, [11]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>pullane</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="D56" s="13" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>D 2 O, [15]</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>PEG [a]</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="D61" s="13" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>D 2 O, [14]</t>
         </is>
@@ -2321,7 +2217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2331,8 +2227,6 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2621,12 +2515,6 @@
         <v>3</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" s="11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2657,14 +2545,6 @@
         <v/>
       </c>
       <c r="G22" s="15">
-        <f>C22-D22*4</f>
-        <v/>
-      </c>
-      <c r="H22" s="15">
-        <f>C22-D22*5</f>
-        <v/>
-      </c>
-      <c r="I22" s="15">
         <f>C22-D22*6</f>
         <v/>
       </c>
@@ -2696,14 +2576,6 @@
         <v/>
       </c>
       <c r="G23" s="15">
-        <f>C23-D23*4</f>
-        <v/>
-      </c>
-      <c r="H23" s="15">
-        <f>C23-D23*5</f>
-        <v/>
-      </c>
-      <c r="I23" s="15">
         <f>C23-D23*6</f>
         <v/>
       </c>
@@ -2735,14 +2607,6 @@
         <v/>
       </c>
       <c r="G24" s="15">
-        <f>C24-D24*4</f>
-        <v/>
-      </c>
-      <c r="H24" s="15">
-        <f>C24-D24*5</f>
-        <v/>
-      </c>
-      <c r="I24" s="15">
         <f>C24-D24*6</f>
         <v/>
       </c>
@@ -2774,14 +2638,6 @@
         <v/>
       </c>
       <c r="G25" s="15">
-        <f>C25-D25*4</f>
-        <v/>
-      </c>
-      <c r="H25" s="15">
-        <f>C25-D25*5</f>
-        <v/>
-      </c>
-      <c r="I25" s="15">
         <f>C25-D25*6</f>
         <v/>
       </c>
@@ -2813,14 +2669,6 @@
         <v/>
       </c>
       <c r="G26" s="15">
-        <f>C26-D26*4</f>
-        <v/>
-      </c>
-      <c r="H26" s="15">
-        <f>C26-D26*5</f>
-        <v/>
-      </c>
-      <c r="I26" s="15">
         <f>C26-D26*6</f>
         <v/>
       </c>
@@ -2830,7 +2678,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>EXTRACTED TABLE DATA</t>
+          <t>EXTRACTED RAW TABLE DATA</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -2863,146 +2711,126 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>benzene-d6</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>7.94 � 0.02</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>8.15 � 0.02</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>0.49 � 0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>CDCl 3</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>7.97 � 0.01</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>8.22 � 0.01</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>0.46 � 0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>acetone-d6</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>7.78 � 0.02</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>8.31 � 0.02</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>0.43 � 0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>toluene-d8</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>7.82 � 0.01</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>8.07 � 0.01</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>0.51 � 0.01</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" s="13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>benzene-d6</t>
+          <t>THF-d8</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>7.94 � 0.02</t>
+          <t>8.07 � 0.01</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>8.15 � 0.02</t>
+          <t>8.40 � 0.01</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>0.49 � 0.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>CDCl 3</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>7.97 � 0.01</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>8.22 � 0.01</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>0.46 � 0.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>acetone-d6</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>7.78 � 0.02</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>8.31 � 0.02</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>0.43 � 0.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>toluene-d8</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>7.82 � 0.01</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>8.07 � 0.01</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>0.51 � 0.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B55" s="12" t="inlineStr">
-        <is>
-          <t>THF-d8</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>8.07 � 0.01</t>
-        </is>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>8.40 � 0.01</t>
-        </is>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>0.42 � 0.02</t>
         </is>
@@ -3039,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3049,8 +2877,6 @@
     <col width="39" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3339,12 +3165,6 @@
         <v>3</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" s="11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3375,14 +3195,6 @@
         <v/>
       </c>
       <c r="G22" s="15">
-        <f>C22-D22*4</f>
-        <v/>
-      </c>
-      <c r="H22" s="15">
-        <f>C22-D22*5</f>
-        <v/>
-      </c>
-      <c r="I22" s="15">
         <f>C22-D22*6</f>
         <v/>
       </c>
@@ -3414,14 +3226,6 @@
         <v/>
       </c>
       <c r="G23" s="15">
-        <f>C23-D23*4</f>
-        <v/>
-      </c>
-      <c r="H23" s="15">
-        <f>C23-D23*5</f>
-        <v/>
-      </c>
-      <c r="I23" s="15">
         <f>C23-D23*6</f>
         <v/>
       </c>
@@ -3453,14 +3257,6 @@
         <v/>
       </c>
       <c r="G24" s="15">
-        <f>C24-D24*4</f>
-        <v/>
-      </c>
-      <c r="H24" s="15">
-        <f>C24-D24*5</f>
-        <v/>
-      </c>
-      <c r="I24" s="15">
         <f>C24-D24*6</f>
         <v/>
       </c>
@@ -3492,14 +3288,6 @@
         <v/>
       </c>
       <c r="G25" s="15">
-        <f>C25-D25*4</f>
-        <v/>
-      </c>
-      <c r="H25" s="15">
-        <f>C25-D25*5</f>
-        <v/>
-      </c>
-      <c r="I25" s="15">
         <f>C25-D25*6</f>
         <v/>
       </c>
@@ -3531,14 +3319,6 @@
         <v/>
       </c>
       <c r="G26" s="15">
-        <f>C26-D26*4</f>
-        <v/>
-      </c>
-      <c r="H26" s="15">
-        <f>C26-D26*5</f>
-        <v/>
-      </c>
-      <c r="I26" s="15">
         <f>C26-D26*6</f>
         <v/>
       </c>
@@ -3570,14 +3350,6 @@
         <v/>
       </c>
       <c r="G27" s="15">
-        <f>C27-D27*4</f>
-        <v/>
-      </c>
-      <c r="H27" s="15">
-        <f>C27-D27*5</f>
-        <v/>
-      </c>
-      <c r="I27" s="15">
         <f>C27-D27*6</f>
         <v/>
       </c>
@@ -3609,14 +3381,6 @@
         <v/>
       </c>
       <c r="G28" s="15">
-        <f>C28-D28*4</f>
-        <v/>
-      </c>
-      <c r="H28" s="15">
-        <f>C28-D28*5</f>
-        <v/>
-      </c>
-      <c r="I28" s="15">
         <f>C28-D28*6</f>
         <v/>
       </c>
@@ -3626,7 +3390,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>EXTRACTED TABLE DATA</t>
+          <t>EXTRACTED RAW TABLE DATA</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -3659,167 +3423,143 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>D 2 O methanol-d4 acetone-d6</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>8.23 � 0.01</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>8.14 � 0.01</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>0.49 � 0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="12" t="inlineStr"/>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>8.06 � 0.01</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>8.32 � 0.01</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>0.45 � 0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr"/>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>7.94 � 0.01</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>8.46 � 0.02</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>0.41 � 0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>THF-d8</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>7.94 � 0.01</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>8.26 � 0.02</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>0.46 � 0.01</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
       <c r="A37" s="13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>D 2 O methanol-d4 acetone-d6</t>
+          <t>CDCl 3</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>8.23 � 0.01</t>
+          <t>8.04 � 0.01</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>8.14 � 0.01</t>
+          <t>8.08 � 0.02</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>0.49 � 0.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" s="12" t="inlineStr"/>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>8.06 � 0.01</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>8.32 � 0.01</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
           <t>0.45 � 0.01</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" s="12" t="inlineStr"/>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>7.94 � 0.01</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>8.46 � 0.02</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>0.41 � 0.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>THF-d8</t>
-        </is>
-      </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>7.94 � 0.01</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>8.26 � 0.02</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>0.46 � 0.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>CDCl 3</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>8.04 � 0.01</t>
-        </is>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>8.08 � 0.02</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>0.45 � 0.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" s="13" t="n">
+    <row r="38">
+      <c r="A38" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>ACN-d3</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>7.88 � 0.01</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>8.34 � 0.03</t>
         </is>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>0.44 � 0.01</t>
         </is>

--- a/reports/test5_summary.xlsx
+++ b/reports/test5_summary.xlsx
@@ -519,8 +519,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="-8.710000000000001"/>
-          <min val="-11.71"/>
+          <max val="-9.109999999999999"/>
+          <min val="-11.31"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -787,8 +787,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="-8.57"/>
-          <min val="-11.38"/>
+          <max val="-8.970000000000001"/>
+          <min val="-10.98"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1125,8 +1125,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="-8.67"/>
-          <min val="-11.67"/>
+          <max val="-9.07"/>
+          <min val="-11.27"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1170,7 +1170,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6480000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1197,7 +1197,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6480000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1224,7 +1224,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="6480000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
